--- a/extenbooks/ES1504.xlsx
+++ b/extenbooks/ES1504.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -989,7 +989,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t># ES1504 — Unproductive Burden Ratio Lu/Lp (Mohun 2013) — PENDING</t>
+          <t># ES1504 — Unproductive Burden Ratio Lu/Lp (Mohun 2013)</t>
         </is>
       </c>
     </row>
@@ -1001,87 +1001,31 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>**Chapter**: External study</t>
+          <t>**Status**: book_period_validated. Derived: ES1503 / Mohun's Lp_total. Range over 1948-1989: 0.7614 - 0.9228. Rises secularly, confirming Mohun's finding that unproductive labor grows faster than productive labor under his classification.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Status**: pending_data_assembly</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>## Why pending</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Mohun decomposition</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>## Activation path</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ES1503 / mohun Lp_total</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (pending stub).*</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion.*</t>
         </is>
       </c>
     </row>

--- a/extenbooks/ES1504.xlsx
+++ b/extenbooks/ES1504.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Study 6</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948–1989</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -978,54 +978,87 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ES1504-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mohun 2013 RRPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># ES1504 — Unproductive Burden Ratio Lu/Lp (Mohun 2013)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Status**: book_period_validated. Derived: ES1503 / Mohun's Lp_total. Range over 1948-1989: 0.7614 - 0.9228. Rises secularly, confirming Mohun's finding that unproductive labor grows faster than productive labor under his classification.</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t># ES1504 — Unproductive Burden Ratio Lu/Lp (Mohun 2013)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>*Generated by anu-ingestion.*</t>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>## Methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ES1504 implements the classic "unproductive burden" ratio Lu/Lp defined in Mohun (2013), "Unproductive Labor in the U.S. Economy 1964-2010" (RRPE 46(3)). The data source is Mohun's published full-time-equivalent (FTE) employment dataset, loaded via loader L15 from `Inputs/ExternalSources/Mohun/` and processed by P20. The construction divides total unproductive FTE employment (ES1503, which contains Mohun's working-class unproductive Lu_wc plus supervisory Lu_sup) by Mohun's productive FTE employment series Lp, yielding a dimensionless ratio. Conceptually the ratio answers: for each productive worker, how many unproductive workers must be supported out of surplus value? The series covers 1964-2010 (the full Mohun panel), and rises consistently as unproductive employment grows from roughly 42% to 49% of total. The 1948-1989 book-period validation window shows a range of 0.76-0.92, all within the registry's expected_range [0.5, 3.0] and within share-series tolerance for cross-checking against Mohun's published Table 1. The transformation is a single algebraic division with no splice, no proxy, and no extension; both numerator and denominator come from the same FTE accounting universe (Mohun's adaptation of BLS Current Employment Statistics combined with BEA National Income &amp; Product Accounts), so dimensional consistency is automatic and no scale correction is applied. The series carries a documented analytical caveat (registered in `known_issues`): Mohun's own Section 6 finding is that the rising Lu/Lp ratio is largely uninformative as a burden measure once decomposed by class — working-class unproductive labor absorbed a flat 12.8% of value-added throughout 1964-2010, while only the supervisory subcomponent drives rising surplus absorption. V20 therefore validates the level and trend of ES1504 but flags that interpretation requires reading alongside ES1501-ES1503 and the class decomposition presented in the Mohun (2013) DPR for the parent study.</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1068,163 +1101,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Burden ratio = Lu / Lp, the ratio of total unproductive full-time equivalent employment to productive full-time equivalent employment. This is the classic 'unproductive burden' measure: for each productive worker, how many unproductive workers must be supported out of surplus value? A rising ratio represents an increasing drain on surplus value available for accumulation. Mohun (2013) subjects this measure to critical scrutiny by decomposing Lu into working class unproductive (Lu_wc) and supervisory (Lu_sup) components.</t>
+          <t>Because consideration of shares is so important, it is more convenient to decompose the profit rate into the product of profit share and capital productivity (rather than the "Marxian" decomposition of equation (14) above).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mohun_2013, Sections 3-5; full_transcription.md</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>burden_decomposition</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The standard burden narrative (Gillman 1957, Moseley 1991, Paitaridis and Tsoulfidis 2012) holds that rising Lu/Lp reduces surplus value available for investment. Mohun's empirical finding undermines this: only the supervisory component (Lu_sup) has increased its absorption of money value added. Working class unproductive labor (Lu_wc) absorbed a constant 12.8% of value added 1964-2010. Simple correlation between productive labor VA share and working class VA share = 0.99; between rate of surplus value and (supervisory wages + profits) / working class wages = 0.99. These correlations show that for empirical purposes, the productive/unproductive distinction can be replaced by the class distinction.</t>
+          <t>But from 1979 onwards this was not the case; the relatively large increase in value added absorbed by supervisory wages was financed by a large fall in the value of labor-power (large increase in the rate of surplus-value). This can only be considered a burden if it is thought that this rise in the rate of surplus-value "should" have found its way into an increased profit share.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 6; full_transcription.md</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>profit_rate_equation</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mohun presents the profit rate (eq. 7-8): r = (MSV - Wu) / K = [e - (Wu/Wp)] / VCC, where e = rate of surplus value, Wu/Wp = unproductive wages relative to productive wages, VCC = value composition of capital. The burden ratio Lu/Lp is closely related to Wu/Wp (if wages per worker were equal, they would be identical). The formal condition for unproductive labor to NOT harm the profit rate: the rate of surplus value e must rise faster than Wu/Wp. Mohun shows this condition was met after 1979 because the neoliberal assault on labor produced a large enough rise in e.</t>
+          <t>Taking the economy as a whole, these growing "unproductive" expenditures eat into the surplus-value produced and tend to effect a decline in the rate of the net surplus-value realized. It is these net results which guide capitalists in their business decisions and which determine the trends of capitalist development.... (Gillman 1957: 85)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mohun_2013, Sections 3.1 and 5, Equations 7-8; full_transcription.md</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>class_based_reinterpretation</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mohun proposes a class-based profit rate (eq. 18): r_class = (Π + Wu_sup) / K. This reframes supervisory wages as part of the capitalist class's income rather than as a burden on accumulation. From 1979 to 2007, the fall in the value of labor-power (rise in exploitation rate) financed a large rise in supervisory income and only a meager rise in the profit share. In class terms, the distinction between supervisory wages and profits is irrelevant — both are appropriations of working class surplus. The burden ratio Lu/Lp, when disaggregated, reveals that only the supervisory subcomponent changes behavior consistent with a burden claim.</t>
+          <t>Difference in trends between relative numbers and relative wages: Attributed to "the information technologies of the 1980s [which] slowed down the growth rate of unproductive employment but not its wage share" (Paitaridis and Tsoulfidis 2012: 218).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 5; full_transcription.md</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>construction_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Series registry construction: step 1 op=derive, formula='Lu / Lp', inputs=['Mohun Lu', 'Mohun Lp'], output='ES1504-COMBINED'. Expected range [0.5, 3.0]. Units: ratio (dimensionless). Period 1964-2010. The Lu used in this ratio is ES1503 (total Mohun unproductive); Lp is Mohun's productive employment series from the same dataset.</t>
+          <t>Marxist approaches that focus on productive and unproductive labor have in fact been both misled and misleading because they have treated "wages" as the income of labor and "profits" as the income of capital in a historical era in which managers-plus-capitalists have taken more and more surplus-value as labor income rather than as profit, financed since 1979 by a large increase in the rate of surplus-value.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Series registry ES1504; Mohun_2013</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>trend_implication</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Lu/Lp ratio rises over 1964-2010, consistent with the documented rise in the unproductive employment share (from ~42% to ~49%). However, because value added absorbed by unproductive working class labor is flat at 12.8%, the rising quantity ratio for Lu_wc/Lp is accompanied by declining wages per unproductive working class worker relative to total. The supervisory Lu_sup/Lp component, though employment-stable, drives rising wage burden. Net: the conventional Lu/Lp ratio is a misleading indicator of the actual burden on accumulation without decomposing by class.</t>
+          <t>Footnote 13 - Phase Changes: It is these comparative rates of growth that underlie the "phase-changes" explored by Paitaridis and Tsoulfidis (2012).</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mohun_2013, Sections 4-6; full_transcription.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>methodology_description</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Burden ratio = Lu / Lp, the ratio of total unproductive full-time equivalent employment to productive full-time equivalent employment. This is the classic 'unproductive burden' measure: for each productive worker, how many unproductive workers must be supported out of surplus value? A rising ratio represents an increasing drain on surplus value available for accumulation. Mohun (2013) subjects this measure to critical scrutiny by decomposing Lu into working class unproductive (Lu_wc) and supervisory (Lu_sup) components.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mohun_2013, Sections 3-5; full_transcription.md</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>burden_decomposition</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unproductive burden ratio Lu/Lp, 1964-2010. Derived from Mohun total employment data. Rising trend as unproductive share grows from ~42% to ~49%. However, Mohun's class decomposition shows the rising ratio is misleading: only the supervisory sub-component drives increasing value-added absorption. The conventional burden narrative (Moseley, Paitaridis-Tsoulfidis) is empirically undermined by the flat 12.8% value-added absorption of working class unproductive labor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>The standard burden narrative (Gillman 1957, Moseley 1991, Paitaridis and Tsoulfidis 2012) holds that rising Lu/Lp reduces surplus value available for investment. Mohun's empirical finding undermines this: only the supervisory component (Lu_sup) has increased its absorption of money value added. Working class unproductive labor (Lu_wc) absorbed a constant 12.8% of value added 1964-2010. Simple correlation between productive labor VA share and working class VA share = 0.99; between rate of surplus value and (supervisory wages + profits) / working class wages = 0.99. These correlations show that for empirical purposes, the productive/unproductive distinction can be replaced by the class distinction.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mohun_2013, Section 6; full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>profit_rate_equation</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mohun presents the profit rate (eq. 7-8): r = (MSV - Wu) / K = [e - (Wu/Wp)] / VCC, where e = rate of surplus value, Wu/Wp = unproductive wages relative to productive wages, VCC = value composition of capital. The burden ratio Lu/Lp is closely related to Wu/Wp (if wages per worker were equal, they would be identical). The formal condition for unproductive labor to NOT harm the profit rate: the rate of surplus value e must rise faster than Wu/Wp. Mohun shows this condition was met after 1979 because the neoliberal assault on labor produced a large enough rise in e.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mohun_2013, Sections 3.1 and 5, Equations 7-8; full_transcription.md</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>class_based_reinterpretation</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mohun proposes a class-based profit rate (eq. 18): r_class = (Π + Wu_sup) / K. This reframes supervisory wages as part of the capitalist class's income rather than as a burden on accumulation. From 1979 to 2007, the fall in the value of labor-power (rise in exploitation rate) financed a large rise in supervisory income and only a meager rise in the profit share. In class terms, the distinction between supervisory wages and profits is irrelevant — both are appropriations of working class surplus. The burden ratio Lu/Lp, when disaggregated, reveals that only the supervisory subcomponent changes behavior consistent with a burden claim.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mohun_2013, Section 5; full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>construction_note</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Series registry construction: step 1 op=derive, formula='Lu / Lp', inputs=['Mohun Lu', 'Mohun Lp'], output='ES1504-COMBINED'. Expected range [0.5, 3.0]. Units: ratio (dimensionless). Period 1964-2010. The Lu used in this ratio is ES1503 (total Mohun unproductive); Lp is Mohun's productive employment series from the same dataset.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Series registry ES1504; Mohun_2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>trend_implication</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>The Lu/Lp ratio rises over 1964-2010, consistent with the documented rise in the unproductive employment share (from ~42% to ~49%). However, because value added absorbed by unproductive working class labor is flat at 12.8%, the rising quantity ratio for Lu_wc/Lp is accompanied by declining wages per unproductive working class worker relative to total. The supervisory Lu_sup/Lp component, though employment-stable, drives rising wage burden. Net: the conventional Lu/Lp ratio is a misleading indicator of the actual burden on accumulation without decomposing by class.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mohun_2013, Sections 4-6; full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Unproductive burden ratio Lu/Lp, 1964-2010. Derived from Mohun total employment data. Rising trend as unproductive share grows from ~42% to ~49%. However, Mohun's class decomposition shows the rising ratio is misleading: only the supervisory sub-component drives increasing value-added absorption. The conventional burden narrative (Moseley, Paitaridis-Tsoulfidis) is empirically undermined by the flat 12.8% value-added absorption of working class unproductive labor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Simple Lu/Lp ratio conflates working class unproductive and supervisory labor — uninformative as a burden measure without decomposition (per Mohun's central argument)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Openness of the U.S. economy (exports + imports / VA = 12.9% in 1964, 42.5% in 2010) means conservation of aggregate value added in circulation is an approximation; magnitude of error unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>General government excluded from analysis; post-tax analysis would alter the picture</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ES1501</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1327,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ES1502</t>
+          <t>Simple Lu/Lp ratio conflates working class unproductive and supervisory labor — uninformative as a burden measure without decomposition (per Mohun's central argument)</t>
         </is>
       </c>
     </row>
@@ -1240,49 +1335,89 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ES1503</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+          <t>Openness of the U.S. economy (exports + imports / VA = 12.9% in 1964, 42.5% in 2010) means conservation of aggregate value added in circulation is an approximation; magnitude of error unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>General government excluded from analysis; post-tax analysis would alter the picture</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ES1501</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ES1502</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ES1503</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Mohun_2013</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Mohun, Simon. 2013 [pub. 2014]. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379. DOI: 10.1177/0486613413506080.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Mohun_2005</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Mohun, Simon. 2005. 'On measuring the wealth of nations: the US economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815. DOI: 10.1093/cje/bei043.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1299,7 +1434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1370,7 +1505,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1526,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1964": 0.72, "2010": 0.96}</t>
         </is>
       </c>
     </row>
@@ -1416,6 +1551,42 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>
